--- a/jpcore-r4/feature/swg2-dental-eCS/CodeSystem-jp-dental-surfacebodystructure-cs.xlsx
+++ b/jpcore-r4/feature/swg2-dental-eCS/CodeSystem-jp-dental-surfacebodystructure-cs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="55">
   <si>
     <t>Property</t>
   </si>
@@ -126,7 +126,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>5</t>
+    <t>6</t>
   </si>
   <si>
     <t>Level</t>
@@ -144,34 +144,40 @@
     <t>1</t>
   </si>
   <si>
-    <t>TP-13-01</t>
+    <t>TP-13</t>
   </si>
   <si>
     <t>切端・咬合面ＩＯ（切端I又は咬合面Ｏ）</t>
   </si>
   <si>
-    <t>TP-14-01</t>
+    <t>TP-14</t>
   </si>
   <si>
     <t>唇側面・頬側面Ｂ（唇側面Ｌａ、頬側面Ｂ又は口腔前庭面Ｖ）</t>
   </si>
   <si>
-    <t>TP-15-01</t>
+    <t>TP-15</t>
   </si>
   <si>
     <t>口蓋側面・舌側面ＰＬ（口蓋側面Ｐ又は舌側面Ｌ（Ｌｉ））</t>
   </si>
   <si>
-    <t>TP-16-01</t>
+    <t>TP-16</t>
   </si>
   <si>
     <t>近心面Ｍ</t>
   </si>
   <si>
-    <t>TP-17-01</t>
+    <t>TP-17</t>
   </si>
   <si>
     <t>遠心面Ｄ</t>
+  </si>
+  <si>
+    <t>TP-18</t>
+  </si>
+  <si>
+    <t>歯冠部</t>
   </si>
 </sst>
 </file>
@@ -483,7 +489,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -560,6 +566,18 @@
       </c>
       <c r="D6" s="2"/>
     </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
